--- a/consent_forms/047_portrait_photography_contract_form--consent_forms.xlsx
+++ b/consent_forms/047_portrait_photography_contract_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -781,12 +781,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>signature</t>
+          <t>signature_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Signature</t>
+          <t>Signature 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -881,12 +881,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>date_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>Date 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -927,12 +927,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>info_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Info 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -950,12 +950,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>info_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Info</t>
+          <t>Info 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -973,12 +973,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>notes_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Notes 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -996,12 +996,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>name_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Name</t>
+          <t>Name 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>status_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Status 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1118,12 +1118,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
@@ -1168,29 +1168,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>terms_of_agreement_choices</t>
+          <t>agreement_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>agreed</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Agreed</t>
         </is>
       </c>
     </row>
@@ -1202,29 +1202,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>agreed</t>
+          <t>disagreed</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Agreed</t>
+          <t>Disagreed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>agreement_choices</t>
+          <t>status_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>disagreed</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Disagreed</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>in_progress</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>In Progress</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
@@ -1253,61 +1253,44 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>completed</t>
+          <t>signed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Completed</t>
+          <t>Signed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>status_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>signed</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Signed</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>status_choices</t>
+          <t>status_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>paid</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
-        <is>
-          <t>Paid</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>status_choices</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>unpaid</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
         <is>
           <t>Unpaid</t>
         </is>
